--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484099_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484099_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1572</v>
+        <v>3.7716</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3422</v>
+        <v>2.2652</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8151</v>
+        <v>1.5064</v>
       </c>
       <c r="G2" t="n">
         <v>0.6499</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3846</v>
+        <v>0.999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8706</v>
+        <v>0.7936</v>
       </c>
       <c r="U2" t="n">
-        <v>0.514</v>
+        <v>0.2053</v>
       </c>
       <c r="V2" t="n">
         <v>0.3373</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0895</v>
+        <v>3.353</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5905</v>
+        <v>1.5735</v>
       </c>
       <c r="F3" t="n">
-        <v>1.499</v>
+        <v>1.7795</v>
       </c>
       <c r="G3" t="n">
         <v>2.5644</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7029</v>
+        <v>0.9664</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6349</v>
+        <v>0.6179</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0679</v>
+        <v>0.3485</v>
       </c>
       <c r="V3" t="n">
         <v>2.0044</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.915</v>
+        <v>2.7539</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3542</v>
+        <v>4.1931</v>
       </c>
       <c r="F4" t="n">
         <v>-1.4391</v>
@@ -766,10 +766,10 @@
         <v>0.5952</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7425</v>
+        <v>0.0964</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7481</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="U4" t="n">
         <v>0.0056</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6495</v>
+        <v>2.5048</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4062</v>
+        <v>4.2055</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7567</v>
+        <v>-1.7006</v>
       </c>
       <c r="G5" t="n">
         <v>2.4299</v>
@@ -844,13 +844,13 @@
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5577</v>
+        <v>0.2976</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1813</v>
+        <v>0.6179</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3765</v>
+        <v>-0.3203</v>
       </c>
       <c r="V5" t="n">
         <v>-1.8097</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2974</v>
+        <v>1.8302</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.638</v>
+        <v>-0.1052</v>
       </c>
       <c r="F6" t="n">
         <v>1.9354</v>
@@ -922,10 +922,10 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.187</v>
+        <v>0.7198</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0452</v>
+        <v>0.4876</v>
       </c>
       <c r="U6" t="n">
         <v>0.2323</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3311</v>
+        <v>-0.1886</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5386</v>
+        <v>0.7653</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8697</v>
+        <v>-0.9539</v>
       </c>
       <c r="G7" t="n">
         <v>0.827</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7147</v>
+        <v>0.8573</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3288</v>
+        <v>0.5555</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3859</v>
+        <v>0.3017</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2777</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5362</v>
+        <v>-3.0042</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4431</v>
+        <v>-1.9112</v>
       </c>
       <c r="F8" t="n">
         <v>-1.093</v>
@@ -1078,10 +1078,10 @@
         <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3127</v>
+        <v>0.8446</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3467</v>
+        <v>0.8786</v>
       </c>
       <c r="U8" t="n">
         <v>-0.034</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2488</v>
+        <v>-3.6763</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4145</v>
+        <v>-1.842</v>
       </c>
       <c r="F9" t="n">
         <v>-1.8343</v>
@@ -1156,10 +1156,10 @@
         <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2721</v>
+        <v>0.3004</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4988</v>
+        <v>0.0737</v>
       </c>
       <c r="U9" t="n">
         <v>0.2267</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.4363</v>
+        <v>-6.5413</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.9743</v>
+        <v>-5.1354</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4621</v>
+        <v>-1.406</v>
       </c>
       <c r="G10" t="n">
         <v>-8.229200000000001</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0169</v>
+        <v>-0.1219</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6744</v>
+        <v>0.1644</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3424</v>
+        <v>-0.2863</v>
       </c>
       <c r="V10" t="n">
         <v>1.8097</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4438000000000004</v>
+        <v>0.8030999999999988</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7618</v>
+        <v>4.008800000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2054</v>
+        <v>-3.2056</v>
       </c>
       <c r="G11" t="n">
         <v>2.0405</v>
@@ -1312,10 +1312,10 @@
         <v>10.9114</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7127</v>
+        <v>4.9596</v>
       </c>
       <c r="T11" t="n">
-        <v>3.033199999999999</v>
+        <v>4.28</v>
       </c>
       <c r="U11" t="n">
         <v>0.6795</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4297</v>
+        <v>6.1737</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8983</v>
+        <v>5.5105</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5314</v>
+        <v>0.6632</v>
       </c>
       <c r="G12" t="n">
         <v>4.3856</v>
@@ -1390,13 +1390,13 @@
         <v>3.3725</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0175</v>
+        <v>-0.2735</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.1756</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2297</v>
+        <v>-0.0979</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1206</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.563</v>
+        <v>3.4856</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5419</v>
+        <v>3.8277</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9789</v>
+        <v>-0.3421</v>
       </c>
       <c r="G13" t="n">
         <v>2.9428</v>
@@ -1468,13 +1468,13 @@
         <v>2.9758</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0392</v>
+        <v>-0.0382</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2414</v>
+        <v>0.5272</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2023</v>
+        <v>-0.5655</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1963</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8416</v>
+        <v>0.2855</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6899</v>
+        <v>1.0777</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-0.7922</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3619</v>
@@ -1546,13 +1546,13 @@
         <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1257</v>
+        <v>0.5697</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1224</v>
+        <v>0.5102</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0034</v>
+        <v>0.0595</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1206</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.1501</v>
       </c>
       <c r="E15" t="n">
         <v>-0.0149</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0247</v>
+        <v>0.165</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4294</v>
@@ -1624,13 +1624,13 @@
         <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1559</v>
+        <v>-0.0156</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1757</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0198</v>
+        <v>0.1601</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4445</v>
+        <v>-0.2404</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5287</v>
+        <v>1.7328</v>
       </c>
       <c r="F16" t="n">
         <v>-1.9732</v>
@@ -1702,10 +1702,10 @@
         <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0543</v>
+        <v>-0.8502</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6858</v>
+        <v>-0.4817</v>
       </c>
       <c r="U16" t="n">
         <v>-0.3685</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5867</v>
+        <v>-0.2424</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0847</v>
+        <v>0.2888</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6715</v>
+        <v>-0.5312</v>
       </c>
       <c r="G17" t="n">
         <v>0.1084</v>
@@ -1780,13 +1780,13 @@
         <v>2.1822</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2328</v>
+        <v>-0.8885</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6008</v>
+        <v>-0.3967</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6321</v>
+        <v>-0.4918</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6526</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. CEBRIA PUCHADES</t>
+          <t>H. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6331</v>
+        <v>-0.6162</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1946</v>
+        <v>-3.1295</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5614</v>
+        <v>2.5133</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8946</v>
+        <v>0.5148</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7209</v>
+        <v>0.459</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6155</v>
+        <v>0.0557</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6079</v>
+        <v>-0.0571</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0806</v>
+        <v>0.5804</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5272</v>
+        <v>-0.6375</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2867</v>
+        <v>0.5718</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8016</v>
+        <v>-0.1214</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0883</v>
+        <v>0.6932</v>
       </c>
       <c r="P18" t="n">
         <v>-0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>-3.1741</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0675</v>
+        <v>-0.0184</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1814</v>
+        <v>-0.1643</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.114</v>
+        <v>0.1459</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6032</v>
+        <v>-0.1206</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6032</v>
+        <v>-0.3866</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. RAMON AÑIBARRO</t>
+          <t>V. CEBRIA PUCHADES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5948</v>
+        <v>-0.719</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.6397</v>
+        <v>-1.5006</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0448</v>
+        <v>0.7817</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5148</v>
+        <v>0.8946</v>
       </c>
       <c r="H19" t="n">
-        <v>0.459</v>
+        <v>-0.7209</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0557</v>
+        <v>1.6155</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0571</v>
+        <v>0.6079</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5804</v>
+        <v>0.0806</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6375</v>
+        <v>0.5272</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5718</v>
+        <v>0.2867</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1214</v>
+        <v>-0.8016</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6932</v>
+        <v>1.0883</v>
       </c>
       <c r="P19" t="n">
         <v>-0.9919</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1741</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.997</v>
+        <v>-0.0184</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6744</v>
+        <v>-0.1247</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3226</v>
+        <v>0.1062</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1206</v>
+        <v>-0.6032</v>
       </c>
       <c r="W19" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3866</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5498</v>
+        <v>-2.128</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2424</v>
+        <v>-0.7322</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3074</v>
+        <v>-1.3958</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2863</v>
@@ -2014,13 +2014,13 @@
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9262</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5498</v>
+        <v>-0.0396</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3765</v>
+        <v>-0.4649</v>
       </c>
       <c r="V20" t="n">
         <v>0.266</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5916</v>
+        <v>-4.3448</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4466</v>
+        <v>-3.8547</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.145</v>
+        <v>-0.4901</v>
       </c>
       <c r="G21" t="n">
         <v>-7.2205</v>
@@ -2092,13 +2092,13 @@
         <v>3.1741</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4387</v>
+        <v>-0.3146</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2495</v>
+        <v>-0.1586</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1891</v>
+        <v>-0.156</v>
       </c>
       <c r="V21" t="n">
         <v>1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4437000000000011</v>
+        <v>1.804099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>3.205300000000001</v>
+        <v>3.205599999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.762</v>
+        <v>-1.4014</v>
       </c>
       <c r="G22" t="n">
         <v>-2.040500000000001</v>
@@ -2170,13 +2170,13 @@
         <v>18.8465</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.7126</v>
+        <v>-2.3522</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6795999999999998</v>
+        <v>-0.6795000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.0334</v>
+        <v>-1.6729</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7382</v>
